--- a/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -926,22 +926,22 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.7291323597580593</v>
+        <v>0.7171286688639856</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.6668434288349496</v>
+        <v>0.6528551478261688</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.7972396143652196</v>
+        <v>0.7877299113272275</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.5433609689648237</v>
+        <v>0.5273554843225526</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.9784177156839051</v>
+        <v>0.975193286113776</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
@@ -1259,19 +1259,19 @@
         <v>9</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.8258022011977293</v>
+        <v>0.8195498933329256</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.6815402286640362</v>
+        <v>0.669984969788664</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1.000600180036005</v>
+        <v>1.002503127605795</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.4707545352261931</v>
+        <v>0.4597556361221974</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.448630282818931</v>
+        <v>1.460910916344895</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>153812</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2243</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="26">
@@ -1551,86 +1551,86 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.1</v>
+        <v>1.148894298164554</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9362244820588583</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+        <v>1.410014516884722</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.6286522322</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.099663439889117</v>
+      </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>120852</v>
+        <v>1766660</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>485</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.148894298164554</v>
+        <v>1.227525064963178</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.9362244820588583</v>
+        <v>0.5259232444453181</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.410014516884722</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.6286522322</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>2.099663439889117</v>
-      </c>
+        <v>2.865377201601115</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>1766660</v>
+        <v>4597</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5212</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.227525064963178</v>
+        <v>1.28</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.5259232444453181</v>
+        <v>0.87</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.865377201601115</v>
+        <v>1.9</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>4597</v>
+        <v>120852</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1909</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37">
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>4.47</v>
+        <v>4.13</v>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
